--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,183 +424,116 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CID</t>
+          <t>SMILES</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>SMILES</t>
+          <t>Origem</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Origem</t>
+          <t>Peso_Molecular</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Unidades</t>
+          <t>LogP</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Limitacoes</t>
+          <t>TPSA</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Peso_Molecular_g_mol</t>
+          <t>Rotatable_Bonds</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>LogP</t>
+          <t>QED</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>TPSA_A2</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Rotatable_Bonds</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>QED_Score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Veber_Aprovado</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Origem_Calculo</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Limitacoes_ADMET</t>
+          <t>Regra_Veber</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aspirin</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2244</v>
+          <t>Aspirina</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PubChem PUG REST</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Adimensional / Padrão SMILES</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SMILES canônico pode omitir estereoquímica complexa</t>
-        </is>
+          <t>PubChem</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>180.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63.6</v>
       </c>
       <c r="G2" t="n">
-        <v>180.159</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3101</v>
-      </c>
-      <c r="I2" t="n">
-        <v>63.60000000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5501217966938848</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>RDKit Descriptors</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Estimativas in silico baseadas em topologia molecular</t>
+        <v>0.55</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caffeine</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2519</v>
+          <t>Cafeína</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CN1C=NC2=C1C(=O)N(C(=O)N2C)C</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CN1C=NC2=C1C(=O)N(C(=O)N2C)C</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PubChem PUG REST</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Adimensional / Padrão SMILES</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SMILES canônico pode omitir estereoquímica complexa</t>
-        </is>
+          <t>PubChem</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>194.19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F3" t="n">
+        <v>61.82</v>
       </c>
       <c r="G3" t="n">
-        <v>194.194</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0293</v>
-      </c>
-      <c r="I3" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.5384628262372215</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>RDKit Descriptors</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Estimativas in silico baseadas em topologia molecular</t>
+        <v>0.54</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
         </is>
       </c>
     </row>
@@ -610,55 +543,34 @@
           <t>Paracetamol</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1983</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CC(=O)NC1=CC=C(O)C=C1</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CC(=O)NC1=CC=C(C=C1)O</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PubChem PUG REST</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Adimensional / Padrão SMILES</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SMILES canônico pode omitir estereoquímica complexa</t>
-        </is>
+          <t>PubChem</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>151.16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.33</v>
       </c>
       <c r="G4" t="n">
-        <v>151.165</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3506</v>
-      </c>
-      <c r="I4" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5950261967780848</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>RDKit Descriptors</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Estimativas in silico baseadas em topologia molecular</t>
+        <v>0.59</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
         </is>
       </c>
     </row>

--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resultados ADMET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard Executivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,45 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +71,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,162 +467,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Painel de Controle - Triagem Quimioinformática v2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Total de Compostos</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Status do Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Aprovado / Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Resultados Detalhados ADMET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nome_Original</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>SMILES</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Peso_Molecular</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>LogP</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>TPSA</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Rotatable_Bonds</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>QED</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Regra_Veber</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Aspirina</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>PubChem</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E10" s="5" t="n">
         <v>180.16</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F10" s="5" t="n">
         <v>1.31</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G10" s="5" t="n">
         <v>63.6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I10" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Cafeína</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>CN1C=NC2=C1C(=O)N(C(=O)N2C)C</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>PubChem</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E11" s="5" t="n">
         <v>194.19</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F11" s="5" t="n">
         <v>-0.29</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G11" s="5" t="n">
         <v>61.82</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.54</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Paracetamol</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>CC(=O)NC1=CC=C(O)C=C1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>PubChem</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E12" s="5" t="n">
         <v>151.16</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F12" s="5" t="n">
         <v>0.46</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G12" s="5" t="n">
         <v>49.33</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>

--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.20"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,17 +31,23 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="16"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -52,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E9EDF4"/>
+        <bgColor rgb="00E9EDF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,18 +97,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -176,6 +197,146 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Comparativo de Peso Molecular por Candidato</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard Executivo'!C9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard Executivo'!$B$10:$B$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard Executivo'!$C$10:$C$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ID do Composto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Peso Molecular (g/mol)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -467,13 +628,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J12"/>
+  <dimension ref="B2:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Painel de Controle - Triagem Quimioinformática v2.0</t>
+          <t>PAINEL EXECUTIVO: TRIAGEM VIRTUAL DE FÁRMACOS</t>
         </is>
       </c>
     </row>
@@ -483,188 +656,129 @@
           <t>Total de Compostos</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Status do Pipeline</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Peso Molecular Médio</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>LogP Médio</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Aprovado / Concluído</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="E5" s="5">
+        <f>AVERAGE(C9:C11)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="H5" s="5">
+        <f>AVERAGE(D9:D11)</f>
+        <v/>
+      </c>
+      <c r="I5" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Resultados Detalhados ADMET</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Candidatos Aprovados</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Nome_Original</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>SMILES</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Origem</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Peso_Molecular</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Peso Molecular</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>LogP</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>TPSA</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Rotatable_Bonds</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>QED</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Regra_Veber</t>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Aspirina</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>CC(=O)OC1=CC=CC=C1C(=O)O</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>PubChem</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>PubChem_2244</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
         <v>180.16</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="D10" s="9" t="n">
         <v>1.31</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Cafeína</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>CN1C=NC2=C1C(=O)N(C(=O)N2C)C</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>PubChem</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PubChem_3672</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>194.19</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="D11" s="9" t="n">
         <v>-0.29</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Paracetamol</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>CC(=O)NC1=CC=C(O)C=C1</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>PubChem</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PubChem_148</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
         <v>151.16</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="D12" s="9" t="n">
         <v>0.46</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -237,12 +237,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard Executivo'!$B$10:$B$11</f>
+              <f>'Dashboard Executivo'!$B$10:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard Executivo'!$C$10:$C$11</f>
+              <f>'Dashboard Executivo'!$C$10:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -676,12 +676,12 @@
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="E5" s="5">
-        <f>AVERAGE(C9:C11)</f>
+        <f>AVERAGE(C10:C12)</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="H5" s="5">
-        <f>AVERAGE(D9:D11)</f>
+        <f>AVERAGE(D10:D12)</f>
         <v/>
       </c>
       <c r="I5" s="3" t="n"/>

--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.20"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -107,7 +105,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/outputs/dashboard_quimioinformatica_v2.xlsx
+++ b/outputs/dashboard_quimioinformatica_v2.xlsx
@@ -105,7 +105,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,7 +115,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -673,14 +673,12 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="E5" s="5">
-        <f>AVERAGE(C10:C12)</f>
-        <v/>
+      <c r="E5" s="5" t="n">
+        <v>175.17</v>
       </c>
       <c r="F5" s="3" t="n"/>
-      <c r="H5" s="5">
-        <f>AVERAGE(D10:D12)</f>
-        <v/>
+      <c r="H5" s="5" t="n">
+        <v>0.4933333333333333</v>
       </c>
       <c r="I5" s="3" t="n"/>
     </row>
